--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +769,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129375390</v>
+      </c>
+      <c r="B3" t="n">
+        <v>86845</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>427</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Puderspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>660839</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6685229</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Sonja Jederlund , Tore Dahlberg, Felicia Wikinger</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86845</v>
+        <v>86848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86848</v>
+        <v>86850</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86850</v>
+        <v>86854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86854</v>
+        <v>86855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86855</v>
+        <v>86883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,6 +801,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormon, Upl</t>
@@ -850,6 +853,11 @@
       </c>
       <c r="AE3" t="b">
         <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86883</v>
+        <v>86889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
+          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86889</v>
+        <v>86890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349667</v>
       </c>
       <c r="B2" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
+          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86890</v>
+        <v>86895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
+          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86895</v>
+        <v>86899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86899</v>
+        <v>86901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,1073 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129922088</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björkholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>660843</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6685226</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129922099</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björkholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>661170</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6685209</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129922082</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björkholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>661024</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6685296</v>
+      </c>
+      <c r="S6" t="n">
+        <v>54</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129922087</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björkholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>661026</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6685175</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129922089</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björkholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>660899</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6685240</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129922085</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>661107</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6685004</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129922097</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>661150</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6684943</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129922074</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98786</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björkholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>661170</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6685238</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En av plantorna har en ny blomstängel på gång!!!</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129922098</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björkholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>661036</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6685114</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1703,7 +1703,7 @@
         <v>129922074</v>
       </c>
       <c r="B11" t="n">
-        <v>98786</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1942,6 +1942,125 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129922090</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>661190</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6685215</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>129922088</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>129922082</v>
       </c>
       <c r="B6" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129922087</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129922089</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129922085</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129922074</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129922090</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86901</v>
+        <v>86904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86904</v>
+        <v>86907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129922088</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>129922082</v>
       </c>
       <c r="B6" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129922087</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129922089</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129922085</v>
       </c>
       <c r="B9" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129922074</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129922090</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86907</v>
+        <v>86908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129922074</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129375390</v>
       </c>
       <c r="B3" t="n">
-        <v>86908</v>
+        <v>86925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>129922082</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129922074</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -1703,7 +1703,7 @@
         <v>129922074</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51522-2025 artfynd.xlsx
+++ b/artfynd/A 51522-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>129922088</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>129922082</v>
       </c>
       <c r="B6" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129922087</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129922089</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129922085</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129922074</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129922090</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
